--- a/data/trans_bre/IP1010-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP1010-Estudios-trans_bre.xlsx
@@ -634,12 +634,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 1,33</t>
+          <t>-3,88; 1,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 0,0</t>
+          <t>-4,24; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 0,15</t>
+          <t>-1,0; 0,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,76</t>
+          <t>-0,68; 0,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,72; -0,19</t>
+          <t>-1,69; -0,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 76,11</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 0,0</t>
+          <t>-2,86; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,3</t>
+          <t>0,0; 1,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 0,0</t>
+          <t>-1,98; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,22 +874,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 0,01</t>
+          <t>-1,1; -0,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 0,47</t>
+          <t>-0,52; 0,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,34; -0,2</t>
+          <t>-1,26; -0,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 166,43</t>
+          <t>-100,0; 92,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 50,95</t>
+          <t>-100,0; 21,55</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1010-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP1010-Estudios-trans_bre.xlsx
@@ -634,12 +634,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 1,3</t>
+          <t>-4,5; 0,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 0,0</t>
+          <t>-3,8; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 0,16</t>
+          <t>-0,99; 0,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 0,73</t>
+          <t>-0,68; 0,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,69; -0,23</t>
+          <t>-1,77; -0,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 0,0</t>
+          <t>-2,81; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,34</t>
+          <t>0,0; 1,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 0,0</t>
+          <t>-2,63; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,1; -0,01</t>
+          <t>-1,05; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 0,46</t>
+          <t>-0,53; 0,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,26; -0,19</t>
+          <t>-1,29; -0,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 92,79</t>
+          <t>-100,0; 82,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 490,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 21,55</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1010-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP1010-Estudios-trans_bre.xlsx
@@ -634,12 +634,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 0,72</t>
+          <t>-4,44; 1,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 0,0</t>
+          <t>-3,82; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 0,16</t>
+          <t>-0,9; 0,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 0,66</t>
+          <t>-0,67; 0,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,77; -0,18</t>
+          <t>-1,72; -0,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 76,11</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 0,0</t>
+          <t>-3,05; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,53</t>
+          <t>0,0; 1,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 0,0</t>
+          <t>-2,65; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 0,0</t>
+          <t>-1,04; 0,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 0,47</t>
+          <t>-0,58; 0,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,29; -0,2</t>
+          <t>-1,34; -0,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 82,47</t>
+          <t>-100,0; 166,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 490,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 50,95</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1010-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP1010-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,137 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-0,84</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-0,75</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-54,31%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+      <c r="C4" s="5" t="n">
+        <v>-0.8395727746013028</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.7463861529527505</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>-0.5431108553265276</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-4,44; 1,33</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-3,82; 0,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-4.443367821891937</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-3.822279633064895</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1.331964571287976</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,28</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,04</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,76</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-65,99%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-10,71%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-87,21%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-0,9; 0,15</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-0,67; 0,76</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-1,72; -0,19</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 76,11</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.2822035697604731</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.04404551943942448</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.7564782795180917</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.6598934024811951</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.1070767880433865</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.872123302634483</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,81</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,27</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,44</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-0.896438582427927</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-0.6679527842239409</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-1.724630170909271</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-3,05; 0,0</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,3</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-2,65; 0,0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.1532852403365935</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.7625041411150855</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>-0.1881371623876375</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="n">
+        <v>0.7611473076655589</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,77 +741,147 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,46</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,06</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,6</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-71,62%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-16,39%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-89,05%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-0.8065428446572515</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.2678300614319545</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.4363081757576793</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-1,04; 0,01</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-0,58; 0,47</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-1,34; -0,2</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 166,43</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 50,95</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-3.053586398887485</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-2.651218371685511</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.29607633048371</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.4620454432963425</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.05808604529367475</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.6046056499110769</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.7161850708478477</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.163909588519952</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.8904629660665447</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.039141576110425</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-0.5752498917497886</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-1.336739166604411</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.009147394509888988</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.473008051981612</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>-0.2048575777734146</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>1.664310887850018</v>
+      </c>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="n">
+        <v>0.5095100806207004</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -913,12 +890,12 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
